--- a/USERS.xlsx
+++ b/USERS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://winsolgroup-my.sharepoint.com/personal/gwenn_vanthournout_winsol_eu/Documents/_Gwenn/DOCS/AI/SOCRATES_WEB_DEV/frontend/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{84D7FD99-9AD4-4647-842E-0F310966C769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{84D7FD99-9AD4-4647-842E-0F310966C769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9841DA15-E32F-4C93-97F6-6F8EAE1509FD}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D8783656-07D5-4FA7-BF25-40044803F138}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
   <si>
     <t>USER</t>
   </si>
@@ -72,16 +72,30 @@
   </si>
   <si>
     <t>WimT01</t>
+  </si>
+  <si>
+    <t>WinsolTest</t>
+  </si>
+  <si>
+    <t>WinsolTest2026!</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -104,13 +118,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -443,7 +460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE8D0455-0C63-4E50-82B6-D8790C5DE6A9}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="20.7109375" customWidth="1"/>
@@ -465,7 +482,7 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C2" t="s">
@@ -505,7 +522,21 @@
         <v>7</v>
       </c>
     </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{757E64E1-101B-4536-B58A-98056608E57D}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/USERS.xlsx
+++ b/USERS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://winsolgroup-my.sharepoint.com/personal/gwenn_vanthournout_winsol_eu/Documents/_Gwenn/DOCS/AI/SOCRATES_WEB_DEV/frontend/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{84D7FD99-9AD4-4647-842E-0F310966C769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9841DA15-E32F-4C93-97F6-6F8EAE1509FD}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{84D7FD99-9AD4-4647-842E-0F310966C769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4DE5AD00-39F7-4F87-B260-0AB4234BE552}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D8783656-07D5-4FA7-BF25-40044803F138}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
   <si>
     <t>USER</t>
   </si>
@@ -78,6 +78,12 @@
   </si>
   <si>
     <t>WinsolTest2026!</t>
+  </si>
+  <si>
+    <t>LodeM</t>
+  </si>
+  <si>
+    <t>LodeAdmin</t>
   </si>
 </sst>
 </file>
@@ -460,7 +466,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE8D0455-0C63-4E50-82B6-D8790C5DE6A9}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="20.7109375" customWidth="1"/>
@@ -533,6 +539,17 @@
         <v>7</v>
       </c>
     </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{757E64E1-101B-4536-B58A-98056608E57D}"/>

--- a/USERS.xlsx
+++ b/USERS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://winsolgroup-my.sharepoint.com/personal/gwenn_vanthournout_winsol_eu/Documents/_Gwenn/DOCS/AI/SOCRATES_WEB_DEV/frontend/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{84D7FD99-9AD4-4647-842E-0F310966C769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4DE5AD00-39F7-4F87-B260-0AB4234BE552}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="8_{84D7FD99-9AD4-4647-842E-0F310966C769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55A23130-DD37-480F-8390-B32DCC8A6398}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D8783656-07D5-4FA7-BF25-40044803F138}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="19">
   <si>
     <t>USER</t>
   </si>
@@ -84,6 +84,18 @@
   </si>
   <si>
     <t>LodeAdmin</t>
+  </si>
+  <si>
+    <t>AnjeB</t>
+  </si>
+  <si>
+    <t>AnjeB02</t>
+  </si>
+  <si>
+    <t>RainerG</t>
+  </si>
+  <si>
+    <t>RainerG03</t>
   </si>
 </sst>
 </file>
@@ -466,7 +478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE8D0455-0C63-4E50-82B6-D8790C5DE6A9}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="20.7109375" customWidth="1"/>
@@ -550,6 +562,28 @@
         <v>4</v>
       </c>
     </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{757E64E1-101B-4536-B58A-98056608E57D}"/>
